--- a/网站内容.xlsx
+++ b/网站内容.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miaomiaojiang/PycharmProjects/dsy/venv/codex/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D2E061-AD37-1249-B4B9-FAA9050CAA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD8928A-8D0F-FC4A-B0CF-D851E4C2CBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="-1360" windowWidth="38400" windowHeight="21000" xr2:uid="{F0E5AE36-DADF-684C-8E45-1043DE7F1EF9}"/>
   </bookViews>
@@ -46,15 +46,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>\textbf{Siyu Duan}. Unraveling Linguistic Variations of Poetry Imagery with Interpretable Embedding by LLM. (forthcoming)</t>
-  </si>
-  <si>
-    <t>\textbf{Siyu Duan}, Jun Wang, Zhaopeng Wang, Qi Su. Quantifying Cultural DNA with Generative Large Language Model. (forthcoming)</t>
-  </si>
-  <si>
-    <t>\textbf{Siyu Duan}. \href{https://arxiv.org/abs/2510.27045}{Quantitative Intertextuality from the Digital Humanities Perspective: A Survey} (forthcoming)</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">\textbf{Siyu Duan}, Jun Wang, Hao Yang, Qi Su. \href{https://www.nature.com/articles/s41599-023-01811-x}{Disentangling the Cultural Evolution of Ancient China: A Digital Humanities Perspective.} </t>
     </r>
@@ -735,6 +726,18 @@
   </si>
   <si>
     <t>段思宇（duansiyv@sjtu.edu.cn），上海交通大学外国语学院，助理教授。北京大学博士，师从\href{https://pkudh.org/member/wangjun.html}{王军}教授与\href{https://pkudh.org/member/suqi.html}{苏祺}副教授，硕士师从\href{https://scholar.google.com.hk/citations?user=tpXiQkYAAAAJ&amp;hl=zh-CN}{孙栩}副教授。长期从事人工智能与人文社科的交叉学科研究，在SSCI、A&amp;HCI期刊和CCF会议上发表多篇高水平论文。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\textbf{Siyu Duan}, Jun Wang, Zhaopeng Wang, Qi Su. Quantifying Cultural DNA with Generative Large Language Model. (under review)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\textbf{Siyu Duan}. Unraveling Linguistic Variations of Poetry Imagery with Interpretable Embedding by LLM. (working paper)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>\textbf{Siyu Duan}. \href{https://arxiv.org/abs/2510.27045}{Quantitative Intertextuality from the Digital Humanities Perspective: A Survey} (under review)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1190,102 +1193,102 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="G1" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="112">
       <c r="A2" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="140">
       <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="70">
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="98">
       <c r="A5" s="3"/>
       <c r="D5" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="70">
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="56">
       <c r="D7" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="56">
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28">
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1306,35 +1309,35 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="409.6">
       <c r="A2" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1350,26 +1353,26 @@
   <sheetData>
     <row r="1" spans="1:2" ht="28">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="345">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1385,24 +1388,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s">
         <v>32</v>
-      </c>
-      <c r="C1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/网站内容.xlsx
+++ b/网站内容.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miaomiaojiang/PycharmProjects/dsy/venv/codex/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96CC8B6-E719-B645-B6A4-165FCC83C0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C022C791-E678-364D-9948-C1C4F692156A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{F0E5AE36-DADF-684C-8E45-1043DE7F1EF9}"/>
+    <workbookView xWindow="-26120" yWindow="1720" windowWidth="22940" windowHeight="14380" activeTab="1" xr2:uid="{F0E5AE36-DADF-684C-8E45-1043DE7F1EF9}"/>
   </bookViews>
   <sheets>
     <sheet name="主页" sheetId="1" r:id="rId1"/>
@@ -500,10 +500,6 @@
     <t>多模态古文字修复</t>
   </si>
   <si>
-    <t>文字修复2.pdf</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>photo.jpg</t>
   </si>
   <si>
@@ -581,6 +577,10 @@
   </si>
   <si>
     <t>本科生：张霁雯，陈如怡，兰巧智</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文字修复1.pdf</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1039,7 +1039,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="2" spans="1:7" ht="84">
       <c r="A2" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>11</v>
@@ -1071,21 +1071,21 @@
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="98">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
@@ -1100,10 +1100,10 @@
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="70">
@@ -1157,7 +1157,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>24</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="2" spans="1:2" ht="404">
       <c r="A2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1176,7 +1176,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1208,13 +1208,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
         <v>33</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/网站内容.xlsx
+++ b/网站内容.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miaomiaojiang/PycharmProjects/dsy/venv/codex/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C022C791-E678-364D-9948-C1C4F692156A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174C4C01-9EC7-A94B-B574-465B2E9E6034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26120" yWindow="1720" windowWidth="22940" windowHeight="14380" activeTab="1" xr2:uid="{F0E5AE36-DADF-684C-8E45-1043DE7F1EF9}"/>
+    <workbookView xWindow="-38400" yWindow="-1960" windowWidth="38400" windowHeight="21600" xr2:uid="{F0E5AE36-DADF-684C-8E45-1043DE7F1EF9}"/>
   </bookViews>
   <sheets>
     <sheet name="主页" sheetId="1" r:id="rId1"/>
@@ -576,11 +576,11 @@
     <t>上海交通大学文科青年人才培育计划，“生成式AI驱动的跨语言诗歌文学计算研究”，主持，2026-</t>
   </si>
   <si>
-    <t>本科生：张霁雯，陈如怡，兰巧智</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>文字修复1.pdf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本科生：\href{https://wendie0219.github.io}{张霁雯}，\href{https://hui336.github.io/}{陈如怡}，\href{https://lanq30721.github.io/}{兰巧智}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1103,7 +1103,7 @@
         <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="70">
@@ -1176,7 +1176,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
